--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-08-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-08-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Celotex_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A8C6A9-F95A-482C-9F3C-9CCBC69464EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A948B6C9-103B-485B-B5EB-D14868EFBDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33240" yWindow="2805" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6120" yWindow="705" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
